--- a/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ETH_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F60BAD84-D900-41FF-81C9-9A05064E8958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ABCDCA6-91DE-4B91-9AAE-65BF02DB1866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -864,13 +864,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH02,S04aH03,S04aH02,S01aH03,S02aH04,S02aH05,S04aH06,S03aH02,S01aH06,S02aH03,S01aH02,S04aH04,S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH06,S03aH05,S03aH08,S04aH07,S03aH03</t>
+    <t>S03aH03,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S04aH05,S04aH08,S02aH02,S04aH03,S04aH06,S04aH02,S01aH03,S03aH04,S03aH02,S02aH04,S02aH05,S02aH06,S03aH05,S03aH08,S04aH07,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH09,S03aH01,S02aH01,S02aH10,S04aH08,S01aH10,S03aH02,S03aH08,S03aH10,S04aH02,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S01aH02,S03aH09,S02aH02,S04aH10</t>
+    <t>S02aH02,S04aH10,S01aH08,S02aH08,S01aH09,S03aH01,S02aH01,S02aH10,S01aH10,S03aH02,S02aH09,S04aH09,S04aH02,S03aH08,S03aH10,S03aH09,S04aH08,S01aH01,S04aH01,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH09,S03aH01,S02aH01,S02aH10,S04aH08,S01aH10,S03aH02,S03aH08,S03aH10,S04aH02,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S01aH02,S03aH09,S02aH02,S04aH10</v>
+        <v>S02aH02,S04aH10,S01aH08,S02aH08,S01aH09,S03aH01,S02aH01,S02aH10,S01aH10,S03aH02,S02aH09,S04aH09,S04aH02,S03aH08,S03aH10,S03aH09,S04aH08,S01aH01,S04aH01,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S02aH02,S04aH03,S04aH02,S01aH03,S02aH04,S02aH05,S04aH06,S03aH02,S01aH06,S02aH03,S01aH02,S04aH04,S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH06,S03aH05,S03aH08,S04aH07,S03aH03</v>
+        <v>S03aH03,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S04aH05,S04aH08,S02aH02,S04aH03,S04aH06,S04aH02,S01aH03,S03aH04,S03aH02,S02aH04,S02aH05,S02aH06,S03aH05,S03aH08,S04aH07,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1593,7 +1593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DA927D-9F71-4F72-8C02-C9E2AB78FC63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93162078-18C2-4CE7-97E2-4BF19E0E39C8}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1731,7 +1731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D28C7A-3832-485D-B660-618946FCE5ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5169C70-2ADF-4975-B8E8-21D5B15B0102}">
   <dimension ref="B9:O1690"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -50273,7 +50273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A441E28B-A160-45DD-9D55-BC00A5FC94BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C231D664-D4A5-4BE6-8565-C7E6A06F9A99}">
   <dimension ref="B9:FT78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -69208,7 +69208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2738B466-733A-4246-A411-B72DFE6B58E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78186ED-8DA4-4142-9E42-EFEE3F638819}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -69798,7 +69798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDD46EF-9629-4B6A-8D11-95E828D80C33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BA66C6-63B1-491B-8C6D-67290E0E9D1C}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70705,7 +70705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088C7BBB-FAF6-41DD-B4B9-0FDF04DAB4A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748AB0F1-B4FB-4D08-BD33-D2BBF33D1FBC}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71172,7 +71172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6961416-119C-423E-873C-CC45583CA186}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FF6ACA-9F87-4246-B0D9-165BAFA00DD1}">
   <dimension ref="B9:E114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71204,7 +71204,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.39223333333333338</v>
+        <v>0.39223333333333327</v>
       </c>
       <c r="E11" t="s">
         <v>282</v>
@@ -71372,7 +71372,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.45539999999999997</v>
+        <v>0.45540000000000003</v>
       </c>
       <c r="E23" t="s">
         <v>282</v>
@@ -72044,7 +72044,7 @@
         <v>37</v>
       </c>
       <c r="D71">
-        <v>0.43906666666666672</v>
+        <v>0.43906666666666666</v>
       </c>
       <c r="E71" t="s">
         <v>282</v>
@@ -72100,7 +72100,7 @@
         <v>37</v>
       </c>
       <c r="D75">
-        <v>0.48066666666666674</v>
+        <v>0.48066666666666663</v>
       </c>
       <c r="E75" t="s">
         <v>282</v>
@@ -72156,7 +72156,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.39950000000000002</v>
+        <v>0.39949999999999997</v>
       </c>
       <c r="E79" t="s">
         <v>282</v>
@@ -72604,7 +72604,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.42776666666666663</v>
+        <v>0.42776666666666668</v>
       </c>
       <c r="E111" t="s">
         <v>282</v>
